--- a/Team-Data/2012-13/1-17-2012-13.xlsx
+++ b/Team-Data/2012-13/1-17-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -784,7 +851,7 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -966,7 +1033,7 @@
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -993,7 +1060,7 @@
         <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1124,7 +1191,7 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1148,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>16</v>
@@ -1172,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>15</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1485,7 +1552,7 @@
         <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1509,7 +1576,7 @@
         <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1755,7 @@
         <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
         <v>4</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
         <v>12</v>
@@ -1879,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
         <v>14</v>
@@ -1888,7 +1955,7 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2025,7 +2092,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2049,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -2117,19 +2184,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="H10" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
         <v>35.9</v>
@@ -2147,25 +2214,25 @@
         <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O10" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.709</v>
+        <v>0.714</v>
       </c>
       <c r="R10" t="n">
         <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T10" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U10" t="n">
         <v>20.3</v>
@@ -2189,25 +2256,25 @@
         <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2216,7 +2283,7 @@
         <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2228,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2243,7 +2310,7 @@
         <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2261,16 +2328,16 @@
         <v>22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2398,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2407,10 +2474,10 @@
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
         <v>22</v>
@@ -2440,7 +2507,7 @@
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>13</v>
@@ -2568,7 +2635,7 @@
         <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>18</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>4</v>
@@ -2598,7 +2665,7 @@
         <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
         <v>23</v>
@@ -2619,13 +2686,13 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>17</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>2</v>
       </c>
       <c r="AD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE13" t="n">
         <v>5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>9</v>
@@ -2780,7 +2847,7 @@
         <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.775</v>
+        <v>0.769</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J14" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,40 +2939,40 @@
         <v>7.3</v>
       </c>
       <c r="M14" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P14" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="R14" t="n">
         <v>11.3</v>
       </c>
       <c r="S14" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W14" t="n">
         <v>10.5</v>
       </c>
       <c r="X14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.5</v>
@@ -2914,19 +2981,19 @@
         <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.8</v>
+        <v>102.1</v>
       </c>
       <c r="AC14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AD14" t="n">
         <v>9</v>
       </c>
-      <c r="AD14" t="n">
-        <v>5</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2941,7 +3008,7 @@
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2965,19 +3032,19 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS14" t="n">
         <v>18</v>
       </c>
-      <c r="AS14" t="n">
-        <v>17</v>
-      </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2992,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.436</v>
+        <v>0.447</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.456</v>
@@ -3054,25 +3121,25 @@
         <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P15" t="n">
         <v>28.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
         <v>45.3</v>
@@ -3081,31 +3148,31 @@
         <v>22.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>103.1</v>
+        <v>103.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3123,10 +3190,10 @@
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3147,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
         <v>4</v>
@@ -3159,19 +3226,19 @@
         <v>13</v>
       </c>
       <c r="AV15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3180,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="n">
         <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>13</v>
@@ -3353,7 +3420,7 @@
         <v>21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,19 +3476,19 @@
         <v>38.2</v>
       </c>
       <c r="J17" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.488</v>
       </c>
       <c r="L17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.387</v>
+        <v>0.391</v>
       </c>
       <c r="O17" t="n">
         <v>17.2</v>
@@ -3430,46 +3497,46 @@
         <v>22.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="S17" t="n">
         <v>30.8</v>
       </c>
       <c r="T17" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="U17" t="n">
         <v>22.4</v>
       </c>
       <c r="V17" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="W17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB17" t="n">
         <v>102.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,7 +3548,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3496,10 +3563,10 @@
         <v>6</v>
       </c>
       <c r="AM17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
         <v>14</v>
@@ -3526,16 +3593,16 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.526</v>
+        <v>0.514</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J18" t="n">
-        <v>86.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.432</v>
@@ -3600,31 +3667,31 @@
         <v>6.1</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O18" t="n">
         <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R18" t="n">
         <v>12.8</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T18" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
@@ -3633,7 +3700,7 @@
         <v>8.5</v>
       </c>
       <c r="X18" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="Y18" t="n">
         <v>4.3</v>
@@ -3642,31 +3709,31 @@
         <v>19.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB18" t="n">
         <v>96.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
       </c>
       <c r="AG18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI18" t="n">
         <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3684,25 +3751,25 @@
         <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
@@ -3717,16 +3784,16 @@
         <v>5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
       </c>
       <c r="BC18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.444</v>
+        <v>0.457</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J19" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="L19" t="n">
         <v>5.6</v>
@@ -3785,31 +3852,31 @@
         <v>18.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.295</v>
+        <v>0.297</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.736</v>
+        <v>0.738</v>
       </c>
       <c r="R19" t="n">
         <v>13.7</v>
       </c>
       <c r="S19" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T19" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U19" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
         <v>7.7</v>
@@ -3824,22 +3891,22 @@
         <v>17.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.8</v>
+        <v>95.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3866,13 +3933,13 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
@@ -3884,28 +3951,28 @@
         <v>5</v>
       </c>
       <c r="AU19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AV19" t="n">
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4036,7 +4103,7 @@
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>16</v>
@@ -4048,7 +4115,7 @@
         <v>9</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>28</v>
@@ -4060,16 +4127,16 @@
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4146,34 +4213,34 @@
         <v>11.2</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O21" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V21" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="W21" t="n">
         <v>8.4</v>
@@ -4194,10 +4261,10 @@
         <v>101.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>5</v>
@@ -4212,13 +4279,13 @@
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,13 +4297,13 @@
         <v>5</v>
       </c>
       <c r="AO21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4245,19 +4312,19 @@
         <v>23</v>
       </c>
       <c r="AT21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU21" t="n">
         <v>26</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4430,13 +4497,13 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>23</v>
@@ -4573,7 +4640,7 @@
         <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
         <v>7</v>
@@ -4582,7 +4649,7 @@
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>17</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4761,7 +4828,7 @@
         <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>20</v>
@@ -4770,7 +4837,7 @@
         <v>18</v>
       </c>
       <c r="AM24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
         <v>10</v>
@@ -4788,19 +4855,19 @@
         <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>23</v>
       </c>
       <c r="AU24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -4847,73 +4914,73 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
         <v>13</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.317</v>
+        <v>0.325</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J25" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M25" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O25" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="P25" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R25" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T25" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V25" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="X25" t="n">
         <v>5.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
         <v>18.2</v>
@@ -4925,7 +4992,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
@@ -4937,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
         <v>10</v>
@@ -4946,19 +5013,19 @@
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN25" t="n">
         <v>27</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
         <v>26</v>
@@ -4970,10 +5037,10 @@
         <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU25" t="n">
         <v>15</v>
@@ -4982,13 +5049,13 @@
         <v>5</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>15</v>
@@ -5143,7 +5210,7 @@
         <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
         <v>13</v>
@@ -5164,7 +5231,7 @@
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5337,10 +5404,10 @@
         <v>29</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>3</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5537,7 +5604,7 @@
         <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
@@ -5680,7 +5747,7 @@
         <v>10</v>
       </c>
       <c r="AM29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN29" t="n">
         <v>20</v>
@@ -5698,7 +5765,7 @@
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5716,7 +5783,7 @@
         <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5844,7 +5911,7 @@
         <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>18</v>
@@ -5853,7 +5920,7 @@
         <v>18</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
         <v>13</v>
@@ -5868,7 +5935,7 @@
         <v>8</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -5892,13 +5959,13 @@
         <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6123,7 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>17</v>
@@ -6074,7 +6141,7 @@
         <v>22</v>
       </c>
       <c r="AW31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-17-2012-13</t>
+          <t>2013-01-17</t>
         </is>
       </c>
     </row>
